--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H3">
         <v>426</v>
